--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -442,7 +442,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -457,15 +457,18 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
       </c>
     </row>
@@ -477,7 +480,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -492,15 +495,18 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
       </c>
     </row>
@@ -512,7 +518,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -527,15 +533,18 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
       </c>
     </row>
@@ -547,7 +556,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -562,15 +571,18 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>קובי בוקעי - Like The End Cover להורדה</v>
       </c>
     </row>
@@ -582,7 +594,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -597,15 +609,18 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>קארין עמוס - תפילות קאבר להורדה</v>
       </c>
     </row>
@@ -617,7 +632,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -632,15 +647,18 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
       </c>
     </row>
@@ -652,7 +670,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -667,15 +685,18 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>נועם דדון - הקסם השחור קאבר להורדה</v>
       </c>
     </row>
@@ -687,7 +708,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -702,15 +723,18 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
       </c>
     </row>
@@ -722,7 +746,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -737,15 +761,18 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
       </c>
     </row>
@@ -757,7 +784,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -772,15 +799,18 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
       </c>
     </row>
@@ -792,7 +822,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -807,15 +837,18 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>ברטין - Seni Dusundum Cover להורדה</v>
       </c>
     </row>
@@ -827,7 +860,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -842,15 +875,18 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
       </c>
     </row>
@@ -862,7 +898,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -877,15 +913,18 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
       </c>
     </row>
@@ -897,7 +936,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -912,15 +951,18 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
       </c>
     </row>
@@ -932,7 +974,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-22</v>
@@ -947,15 +989,18 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>מידד טסה - עוף מוזר קאבר להורדה</v>
       </c>
     </row>
@@ -967,7 +1012,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-22</v>
@@ -982,15 +1027,18 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
       </c>
     </row>
@@ -1002,7 +1050,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-22</v>
@@ -1017,15 +1065,18 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
       </c>
     </row>
@@ -1037,7 +1088,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-22</v>
@@ -1052,15 +1103,18 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>דניאל חן - אל תלכי קאבר להורדה</v>
       </c>
     </row>
@@ -1072,7 +1126,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-22</v>
@@ -1087,15 +1141,18 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>איימי - אהבה רעילה קאבר להורדה</v>
       </c>
     </row>
@@ -1107,7 +1164,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-22</v>
@@ -1122,15 +1179,18 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
       </c>
     </row>
@@ -1142,7 +1202,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-22</v>
@@ -1157,15 +1217,18 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>שני פונה - דרך חדשה קאבר להורדה</v>
       </c>
     </row>
@@ -1177,7 +1240,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-22</v>
@@ -1192,15 +1255,18 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>פארידה - Darixdim Cover להורדה</v>
       </c>
     </row>
@@ -1212,7 +1278,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409185&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-22</v>
@@ -1227,15 +1293,18 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>עומרי פרחן - השיר שאת אהבת קאבר להורדה</v>
       </c>
     </row>
@@ -1247,7 +1316,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409184&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-22</v>
@@ -1262,15 +1331,18 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>נתנאל נגר - כל יום שעובר קאבר להורדה</v>
       </c>
     </row>
@@ -1282,7 +1354,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409183&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-22</v>
@@ -1297,15 +1369,18 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>נאור מתתיהו - תמיד שמח קאבר להורדה</v>
       </c>
     </row>
@@ -1317,7 +1392,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409182&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-22</v>
@@ -1332,15 +1407,18 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>לירוי בר זוהר - אבא קאבר להורדה</v>
       </c>
     </row>
@@ -1352,7 +1430,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409181&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-22</v>
@@ -1367,15 +1445,18 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>ליאן אברהם - כשאת עצובה קאבר להורדה</v>
       </c>
     </row>
@@ -1387,7 +1468,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409180&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-22</v>
@@ -1402,15 +1483,18 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>יאיר יראי - תופס לך את הדמעות קאבר להורדה</v>
       </c>
     </row>
@@ -1422,7 +1506,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409179&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-22</v>
@@ -1437,15 +1521,18 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>ברק לוי - לאהוב אותך כל יום קאבר להורדה</v>
       </c>
     </row>
@@ -1457,7 +1544,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=5b742797df25a8700ca67de001cb74b9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409178&amp;sid=06da2f18b29bd92862c21942dabc8718</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-22</v>
@@ -1472,21 +1559,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>ברטין - שביל האושר קאבר להורדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,7 +442,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-23</v>
@@ -480,7 +480,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-23</v>
@@ -518,7 +518,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-23</v>
@@ -556,7 +556,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-23</v>
@@ -594,7 +594,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-23</v>
@@ -632,7 +632,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-23</v>
@@ -670,7 +670,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-23</v>
@@ -708,7 +708,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=28578d22d6bc8863a18a652dcec3ff77</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-23</v>
@@ -738,9 +738,845 @@
         <v>אבירם ברמי - איפה את קאבר להורדה</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>קובי בוקעי - Like The End Cover להורדה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>קובי בוקעי - Like The End Cover להורדה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>קארין עמוס - תפילות קאבר להורדה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>קארין עמוס - תפילות קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ברטין - Seni Dusundum Cover להורדה</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>ברטין - Seni Dusundum Cover להורדה</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C27" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C28" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>איימי - אהבה רעילה קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C29" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C30" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>פארידה - Darixdim Cover להורדה</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>פארידה - Darixdim Cover להורדה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון ביטון - תפילות קאבר להורדה</v>
+        <v>שמעון ביטון - תפילות קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון ביטון - תפילות קאבר להורדה</v>
+        <v>שמעון ביטון - תפילות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
+        <v>נריה עובדיה - ילדה של אב קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נריה עובדיה - ילדה של אב קאבר להורדה</v>
+        <v>נריה עובדיה - ילדה של אב קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
+        <v>נועם דדון - זר של נרקיסים קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - זר של נרקיסים קאבר להורדה</v>
+        <v>נועם דדון - זר של נרקיסים קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
+        <v>יהונתן נחמיאס - מאשאפ חופות 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יהונתן נחמיאס - מאשאפ חופות 2026 להורדה</v>
+        <v>יהונתן נחמיאס - מאשאפ חופות 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
+        <v>חנוך שובל - עולם בשני צבעים קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>חנוך שובל - עולם בשני צבעים קאבר להורדה</v>
+        <v>חנוך שובל - עולם בשני צבעים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>חן גז - אהבה חולה קאבר להורדה</v>
+        <v>חן גז - אהבה חולה קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>חן גז - אהבה חולה קאבר להורדה</v>
+        <v>חן גז - אהבה חולה קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
+        <v>אוריאל שלום - אשת חיל שלי קאבר</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוריאל שלום - אשת חיל שלי קאבר להורדה</v>
+        <v>אוריאל שלום - אשת חיל שלי קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבירם ברמי - איפה את קאבר להורדה</v>
+        <v>אבירם ברמי - איפה את קאבר</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבירם ברמי - איפה את קאבר להורדה</v>
+        <v>אבירם ברמי - איפה את קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר להורדה</v>
+        <v>אביהוא רווח &amp; רועי זקס - כאב של לוחמים קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>תמיר חג'בי - לוותר עלינו ככה קאבר להורדה</v>
+        <v>תמיר חג'בי - לוותר עלינו ככה קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+        <v>רון חטיבי - גודל הכאב קאבר</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>רון חטיבי - גודל הכאב קאבר להורדה</v>
+        <v>רון חטיבי - גודל הכאב קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>קובי בוקעי - Like The End Cover להורדה</v>
+        <v>קובי בוקעי - Like The End Cover</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>קובי בוקעי - Like The End Cover להורדה</v>
+        <v>קובי בוקעי - Like The End Cover</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>קארין עמוס - תפילות קאבר להורדה</v>
+        <v>קארין עמוס - תפילות קאבר</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>קארין עמוס - תפילות קאבר להורדה</v>
+        <v>קארין עמוס - תפילות קאבר</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+        <v>עילאי גניש - מצייר אותך קאבר</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>עילאי גניש - מצייר אותך קאבר להורדה</v>
+        <v>עילאי גניש - מצייר אותך קאבר</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+        <v>נועם דדון - הקסם השחור קאבר</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>נועם דדון - הקסם השחור קאבר להורדה</v>
+        <v>נועם דדון - הקסם השחור קאבר</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+        <v>מתנאל סבח - עד יום מותי קאבר</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>מתנאל סבח - עד יום מותי קאבר להורדה</v>
+        <v>מתנאל סבח - עד יום מותי קאבר</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+        <v>ליה נחום - בסיבוב הבא קאבר</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>ליה נחום - בסיבוב הבא קאבר להורדה</v>
+        <v>ליה נחום - בסיבוב הבא קאבר</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+        <v>ליאל גוטמן - אצלנו בגן קאבר</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>ליאל גוטמן - אצלנו בגן קאבר להורדה</v>
+        <v>ליאל גוטמן - אצלנו בגן קאבר</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ברטין - Seni Dusundum Cover להורדה</v>
+        <v>ברטין - Seni Dusundum Cover</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>ברטין - Seni Dusundum Cover להורדה</v>
+        <v>ברטין - Seni Dusundum Cover</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+        <v>אביחי טהיא - שביל האושר קאבר</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-20</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>אביחי טהיא - שביל האושר קאבר להורדה</v>
+        <v>אביחי טהיא - שביל האושר קאבר</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>עידו עמדור - אהבה ממבט ראשון קאבר להורדה</v>
+        <v>עידו עמדור - אהבה ממבט ראשון קאבר</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>עדיאל - אל תעזוב אותי קאבר להורדה</v>
+        <v>עדיאל - אל תעזוב אותי קאבר</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>מידד טסה - עוף מוזר קאבר להורדה</v>
+        <v>מידד טסה - עוף מוזר קאבר</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>יהונתן חוטה - האישה של חיי קאבר להורדה</v>
+        <v>יהונתן חוטה - האישה של חיי קאבר</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>יהונתן דהן - אהיה לך אושר קאבר להורדה</v>
+        <v>יהונתן דהן - אהיה לך אושר קאבר</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>דניאל חן - אל תלכי קאבר להורדה</v>
+        <v>דניאל חן - אל תלכי קאבר</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>איימי - אהבה רעילה קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-16</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>איימי - אהבה רעילה קאבר להורדה</v>
+        <v>איימי - אהבה רעילה קאבר</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר להורדה</v>
+        <v>רועי מזוז &amp; שילה אלעזר - גג &amp; כלום לא ממכר כמוך קאבר</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>שני פונה - דרך חדשה קאבר להורדה</v>
+        <v>שני פונה - דרך חדשה קאבר</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
       <c r="B31" t="str">
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=160d2f3e0e9b067ae58ac8272b95a67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1571,7 +1571,7 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>פארידה - Darixdim Cover להורדה</v>
+        <v>פארידה - Darixdim Cover</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -442,7 +442,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-24</v>
@@ -480,7 +480,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-24</v>
@@ -518,7 +518,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-24</v>
@@ -556,7 +556,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-24</v>
@@ -594,7 +594,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-24</v>
@@ -632,7 +632,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-24</v>
@@ -670,7 +670,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-24</v>
@@ -708,7 +708,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-24</v>
@@ -746,7 +746,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-24</v>
@@ -784,7 +784,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-24</v>
@@ -822,7 +822,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-24</v>
@@ -860,7 +860,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-24</v>
@@ -898,7 +898,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-24</v>
@@ -936,7 +936,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-24</v>
@@ -974,7 +974,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-24</v>
@@ -1012,7 +1012,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-24</v>
@@ -1050,7 +1050,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-24</v>
@@ -1088,7 +1088,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-24</v>
@@ -1126,7 +1126,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-24</v>
@@ -1164,7 +1164,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-24</v>
@@ -1202,7 +1202,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-24</v>
@@ -1240,7 +1240,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-24</v>
@@ -1278,7 +1278,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-24</v>
@@ -1316,7 +1316,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-24</v>
@@ -1354,7 +1354,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-24</v>
@@ -1392,7 +1392,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-24</v>
@@ -1430,7 +1430,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-24</v>
@@ -1468,7 +1468,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-24</v>
@@ -1506,7 +1506,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-24</v>
@@ -1544,7 +1544,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=2308b59cf0a4f0ec73aa0b57e43927ed</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-24</v>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -442,7 +442,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409337&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-24</v>
@@ -480,7 +480,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409336&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-24</v>
@@ -518,7 +518,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409335&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-24</v>
@@ -556,7 +556,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409334&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-24</v>
@@ -594,7 +594,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409333&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-24</v>
@@ -632,7 +632,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409332&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-24</v>
@@ -670,7 +670,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409331&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-24</v>
@@ -708,7 +708,7 @@
         <v>2026-01-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409330&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-24</v>
@@ -746,7 +746,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409298&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-24</v>
@@ -784,7 +784,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409286&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-24</v>
@@ -822,7 +822,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409285&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-24</v>
@@ -860,7 +860,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409284&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-24</v>
@@ -898,7 +898,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409283&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-24</v>
@@ -936,7 +936,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409282&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-24</v>
@@ -974,7 +974,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409281&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-24</v>
@@ -1012,7 +1012,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409280&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-24</v>
@@ -1050,7 +1050,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409279&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-24</v>
@@ -1088,7 +1088,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409278&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-24</v>
@@ -1126,7 +1126,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409277&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-24</v>
@@ -1164,7 +1164,7 @@
         <v>2026-01-20</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409276&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-24</v>
@@ -1202,7 +1202,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409231&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-24</v>
@@ -1240,7 +1240,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409230&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-24</v>
@@ -1278,7 +1278,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409229&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-24</v>
@@ -1316,7 +1316,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409228&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-24</v>
@@ -1354,7 +1354,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409227&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-24</v>
@@ -1392,7 +1392,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409226&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-24</v>
@@ -1430,7 +1430,7 @@
         <v>2026-01-16</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409225&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-24</v>
@@ -1468,7 +1468,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409188&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-24</v>
@@ -1506,7 +1506,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409187&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-24</v>
@@ -1544,7 +1544,7 @@
         <v>2026-01-13</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=0419c5b15a5fec0ea96adfd515344cb0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409186&amp;sid=4c20a8a3b548565b2fe8531e8fa6a5ab</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-24</v>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עילאי בודאני - תמיד שמח &amp; ציפור זרה קאבר</v>
+        <v>בן חן - Napiyosun Mesela Cover</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409362&amp;sid=c435c2a5a44d5ce4653fe25328d0c6bc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409387&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עילאי בודאני - תמיד שמח &amp; ציפור זרה קאבר</v>
+        <v>בן חן - Napiyosun Mesela Cover</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409386&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409385&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן חן - Napiyosun Mesela Cover</v>
+        <v>רועי יעקב - גיבור של אמא קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409387&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409399&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-28</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן חן - Napiyosun Mesela Cover</v>
+        <v>רועי יעקב - גיבור של אמא קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+        <v>קובי בוקעי - Daydreaming Cover</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-28</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409386&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409398&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-28</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אלקנה אלפסי - ירושלים שלי לעד קאבר</v>
+        <v>קובי בוקעי - Daydreaming Cover</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
+        <v>נחמן סבג - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-28</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409385&amp;sid=3bb702722a537be5a4a84b91629e3914</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409397&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-28</v>
@@ -545,12 +545,354 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלון מיכאל - אל תעזבי אותי קאבר</v>
+        <v>נחמן סבג - אל תעזוב אותי קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מתנאל סבח - כשאחר קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409396&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מתנאל סבח - כשאחר קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאי רובין - עד מחר קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409395&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאי רובין - עד מחר קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יוסף כהן - ירח בננה קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409394&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יוסף כהן - ירח בננה קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יגאל עדי - הבטחות שווא קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409393&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יגאל עדי - הבטחות שווא קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יאיר יראי - תמיד שמח קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409392&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יאיר יראי - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>טל ועקנין &amp; העבריים מדימונה - לכל אחד יש קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409391&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>טל ועקנין &amp; העבריים מדימונה - לכל אחד יש קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>חנוך שובל &amp; עילאי אלול - תמיד שמח קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409390&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>חנוך שובל &amp; עילאי אלול - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חיים איפרגן - לא כמו פעם קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409389&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חיים איפרגן - לא כמו פעם קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>גל וקנין - הנך יפה קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409388&amp;sid=9e98f22eed10f6c90c886f7d605c5409</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>גל וקנין - הנך יפה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>